--- a/partner_results/unknown_complete/ClassesWithMultipleEnglishLabels_unknown.xlsx
+++ b/partner_results/unknown_complete/ClassesWithMultipleEnglishLabels_unknown.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sandwich core | sandwich core role</t>
+          <t>sandwich sheet | sandwich sheet role</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,7 +457,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>a lightweight, low-density material that maintains the separation of face sheets and withstands transverse shear stresses</t>
+          <t>a stiff, strong material that carries bending loads through tensile and compressive stresses when integrated into a panel assembly</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sandwich sheet | sandwich sheet role</t>
+          <t>nonlinear optical property | optical non-linearity</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>optical property</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>a stiff, strong material that carries bending loads through tensile and compressive stresses when integrated into a panel assembly</t>
+          <t>Optical property that is dependent on the intensity of the input light.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -503,18 +503,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nonlinear optical property | optical non-linearity</t>
+          <t>sandwich core role | sandwich core</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>optical property</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Optical property that is dependent on the intensity of the input light.</t>
+          <t>a lightweight, low-density material that maintains the separation of face sheets and withstands transverse shear stresses</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
